--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,112 +1136,112 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 31764-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>LUND</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1141,140 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2059,6 +2059,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2095,42 +2100,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2154,7 +2159,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,7 +2277,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2287,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2296,58 +2301,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2357,14 +2362,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2376,19 +2381,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2418,39 +2418,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2589,11 +2589,6 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2630,42 +2625,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2684,7 @@
         <v>46189</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2772,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2787,14 +2782,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2806,14 +2801,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2831,51 +2831,51 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>46073</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3162,13 +3162,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>20.7</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3211,7 +3206,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3225,10 +3220,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45691</v>
+        <v>44749</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3241,7 +3236,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3284,7 +3279,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3298,10 +3293,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44909</v>
+        <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3313,8 +3308,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>20.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46073</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45985</v>
+        <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45065</v>
+        <v>44846</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46139</v>
+        <v>45065</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45118</v>
+        <v>46244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3751,13 +3751,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3800,7 +3795,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3814,10 +3809,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44649</v>
+        <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3829,8 +3824,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3883,14 +3883,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44749</v>
+        <v>45036</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46244</v>
+        <v>44909</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45189</v>
+        <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4165,7 +4165,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45105</v>
+        <v>45118</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4194,8 +4194,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4238,7 +4243,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4252,10 +4257,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46210</v>
+        <v>45105</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4267,13 +4272,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>45210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45036</v>
+        <v>45189</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 31764-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45688</v>
+        <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1089,23 +1089,28 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1114,21 +1119,129 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
         <v>7</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1136,145 +1249,32 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 72269-2021</t>
+          <t>A 10617-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44543</v>
+        <v>45721</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,17 +1533,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1573,43 +1573,43 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra
-Stor häxört</t>
+          <t>Lökgroda
+Strandpadda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10617-2025</t>
+          <t>A 72269-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45721</v>
+        <v>44543</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1679,36 +1679,36 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lökgroda
-Strandpadda</t>
+          <t>Blanksvart trämyra
+Stor häxört</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45373</v>
+        <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,22 +2277,22 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2304,55 +2304,55 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2362,14 +2362,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2381,14 +2381,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2418,39 +2423,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2479,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2567,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2595,13 +2600,13 @@
         <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2616,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2628,46 +2633,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2681,10 +2686,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46189</v>
+        <v>45373</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2697,7 +2702,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2712,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2721,58 +2726,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,14 +2787,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2801,19 +2806,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2843,39 +2843,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46073</v>
+        <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3206,7 +3206,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44749</v>
+        <v>45751</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3296,7 +3296,7 @@
         <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>45691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>44909</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44846</v>
+        <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45065</v>
+        <v>45985</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46244</v>
+        <v>45189</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46210</v>
+        <v>45105</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3824,13 +3824,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3873,7 +3868,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3883,14 +3878,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45036</v>
+        <v>45065</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3946,7 +3941,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45751</v>
+        <v>46073</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3976,7 +3971,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4019,7 +4014,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4033,10 +4028,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44909</v>
+        <v>45210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4049,7 +4044,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4092,7 +4087,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4106,10 +4101,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44649</v>
+        <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4122,7 +4117,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4182,7 +4177,7 @@
         <v>45118</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4243,7 +4238,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4257,10 +4252,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45105</v>
+        <v>44649</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4273,7 +4268,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4316,7 +4311,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4326,14 +4321,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45210</v>
+        <v>45036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4346,7 +4341,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4389,7 +4384,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4403,10 +4398,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45189</v>
+        <v>46210</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4418,8 +4413,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 31764-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45118</v>
+        <v>45688</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1089,51 +1089,159 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
       </c>
       <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1141,140 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 10617-2025</t>
+          <t>A 72269-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45721</v>
+        <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1573,43 +1573,43 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Lökgroda
-Strandpadda</t>
+          <t>Blanksvart trämyra
+Stor häxört</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 72269-2021</t>
+          <t>A 10617-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44543</v>
+        <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1639,17 +1639,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1679,36 +1679,36 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra
-Stor häxört</t>
+          <t>Lökgroda
+Strandpadda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45104</v>
+        <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,22 +2277,22 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2304,55 +2304,55 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2362,14 +2362,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2381,19 +2381,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2423,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2476,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45988</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2492,16 +2487,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2516,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2528,46 +2523,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46189</v>
+        <v>45988</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2597,13 +2592,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2637,42 +2632,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2686,10 +2681,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45373</v>
+        <v>46189</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2702,7 +2697,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2717,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,58 +2721,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2787,14 +2782,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2806,14 +2801,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2843,39 +2843,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45751</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3235,8 +3235,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>20.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3279,7 +3284,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3293,10 +3298,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45517</v>
+        <v>46073</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3308,13 +3313,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>20.7</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45691</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46139</v>
+        <v>44846</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45985</v>
+        <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45985</v>
+        <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3732,14 +3732,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45189</v>
+        <v>45036</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45105</v>
+        <v>45751</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45065</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46073</v>
+        <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45210</v>
+        <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4043,8 +4043,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4104,7 +4109,7 @@
         <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4174,10 +4179,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45118</v>
+        <v>46210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4195,7 +4200,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4238,7 +4243,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4252,10 +4257,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44649</v>
+        <v>45105</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4268,7 +4273,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4311,7 +4316,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4321,14 +4326,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45036</v>
+        <v>45210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4341,7 +4346,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4384,7 +4389,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4398,10 +4403,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46210</v>
+        <v>45189</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4413,13 +4418,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2059,11 +2059,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2100,49 +2095,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2152,14 +2147,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2171,14 +2166,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2208,46 +2208,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45373</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2301,58 +2301,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45688</v>
+        <v>45889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,13 +2490,13 @@
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2523,39 +2523,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
         <v>45988</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2694,19 +2694,24 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>0.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2721,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2730,49 +2735,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2782,14 +2787,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2801,19 +2806,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2831,51 +2831,51 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44749</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3162,8 +3162,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>20.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3206,7 +3211,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3220,10 +3225,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>45691</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3235,13 +3240,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>20.7</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
         <v>46073</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>44909</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44846</v>
+        <v>45065</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45065</v>
+        <v>45118</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3605,8 +3605,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3649,7 +3654,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3663,10 +3668,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46139</v>
+        <v>44649</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3679,7 +3684,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3722,7 +3727,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3732,14 +3737,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45036</v>
+        <v>46244</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3752,7 +3757,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3795,7 +3800,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3809,10 +3814,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45751</v>
+        <v>45985</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3825,7 +3830,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3868,7 +3873,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3898,7 +3903,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3941,7 +3946,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3955,10 +3960,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44649</v>
+        <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3971,7 +3976,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4014,7 +4019,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4028,10 +4033,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45118</v>
+        <v>46210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4049,7 +4054,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4092,7 +4097,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4106,10 +4111,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46244</v>
+        <v>45751</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4122,7 +4127,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4165,7 +4170,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4179,10 +4184,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46210</v>
+        <v>45189</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4194,13 +4199,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>45105</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45189</v>
+        <v>45036</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,253 +1249,32 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2059,6 +2059,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2095,49 +2100,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2147,14 +2152,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2166,19 +2171,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2196,58 +2196,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,16 +2277,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2313,39 +2313,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>45889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46189</v>
+        <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2527,42 +2527,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45988</v>
+        <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2632,42 +2632,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2677,14 +2677,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2702,16 +2702,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2735,49 +2735,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45373</v>
+        <v>45688</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2831,51 +2831,51 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3162,13 +3162,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>20.7</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3211,7 +3206,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3225,10 +3220,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45691</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3240,8 +3235,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>20.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3284,7 +3284,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46073</v>
+        <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44909</v>
+        <v>44846</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3430,7 +3430,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46139</v>
+        <v>45065</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45065</v>
+        <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45118</v>
+        <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3605,13 +3605,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3654,7 +3649,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3664,14 +3659,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44649</v>
+        <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3684,7 +3679,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3727,7 +3722,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3741,10 +3736,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46244</v>
+        <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3757,7 +3752,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3800,7 +3795,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3814,10 +3809,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45985</v>
+        <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3830,7 +3825,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3873,7 +3868,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45985</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3946,7 +3941,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44749</v>
+        <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3976,7 +3971,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4019,7 +4014,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4033,10 +4028,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46210</v>
+        <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4054,7 +4049,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4097,7 +4092,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4111,10 +4106,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45751</v>
+        <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4127,7 +4122,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4170,7 +4165,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4184,10 +4179,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45189</v>
+        <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4200,7 +4195,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4243,7 +4238,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4257,10 +4252,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45105</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4273,7 +4268,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4316,7 +4311,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45210</v>
+        <v>46210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4345,8 +4340,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4389,7 +4389,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4399,14 +4399,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45036</v>
+        <v>45189</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45688</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45688</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44846</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45065</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>46210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>45189</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45688</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45104</v>
+        <v>45889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,16 +2277,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45889</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2418,39 +2418,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>45688</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>46139</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44846</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>45065</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45036</v>
+        <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3732,14 +3732,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45751</v>
+        <v>45036</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46073</v>
+        <v>45751</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45118</v>
+        <v>46210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46244</v>
+        <v>45118</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4121,8 +4121,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4182,7 +4187,7 @@
         <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4260,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4311,7 +4316,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4325,10 +4330,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46210</v>
+        <v>45189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4340,13 +4345,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4389,7 +4389,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45189</v>
+        <v>46244</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 31764-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,20 +981,25 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1009,7 +1014,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1021,6 +1026,114 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,145 +1141,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45688</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2061,22 +2061,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2091,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2100,49 +2095,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45373</v>
+        <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,22 +2167,22 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2199,55 +2194,55 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,14 +2271,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2418,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45988</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,17 +2486,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2511,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2520,49 +2525,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46189</v>
+        <v>45688</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2592,7 +2597,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2632,42 +2637,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2677,14 +2682,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,19 +2701,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,58 +2726,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45688</v>
+        <v>46189</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2847,35 +2847,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44749</v>
+        <v>45065</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46139</v>
+        <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3313,8 +3313,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3357,7 +3362,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3371,10 +3376,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3387,7 +3392,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3430,7 +3435,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3444,10 +3449,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45065</v>
+        <v>44649</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3460,7 +3465,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3503,7 +3508,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3517,10 +3522,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45985</v>
+        <v>44909</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3533,7 +3538,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3593,7 +3598,7 @@
         <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3649,7 +3654,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3663,10 +3668,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46073</v>
+        <v>45985</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3679,7 +3684,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3722,7 +3727,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3732,14 +3737,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45036</v>
+        <v>44749</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3752,7 +3757,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3812,7 +3817,7 @@
         <v>45751</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3868,7 +3873,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3898,7 +3903,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3941,7 +3946,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3955,10 +3960,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44649</v>
+        <v>46073</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3971,7 +3976,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4014,7 +4019,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4028,10 +4033,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46210</v>
+        <v>45189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4043,13 +4048,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45118</v>
+        <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4121,13 +4121,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4170,7 +4165,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4184,10 +4179,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45105</v>
+        <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4200,7 +4195,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4243,7 +4238,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4253,14 +4248,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>45036</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4273,7 +4268,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4316,7 +4311,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45189</v>
+        <v>46139</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4346,7 +4341,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4389,7 +4384,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4403,10 +4398,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46244</v>
+        <v>46210</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4418,8 +4413,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31764-2023</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45118</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,25 +981,20 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1014,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1026,6 +1021,119 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1033,140 +1141,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45688</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44464</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2061,17 +2061,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2086,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2095,49 +2100,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45104</v>
+        <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,22 +2172,22 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2194,55 +2199,55 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2252,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2271,19 +2276,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45988</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2418,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,22 +2486,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2516,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2525,49 +2520,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45688</v>
+        <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2597,7 +2592,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2637,42 +2632,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2682,14 +2677,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2701,14 +2696,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,58 +2726,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46189</v>
+        <v>45688</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2847,35 +2847,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         <v>44679</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44525</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45065</v>
+        <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45118</v>
+        <v>44846</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3313,13 +3313,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3362,7 +3357,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3376,10 +3371,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45691</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3392,7 +3387,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3435,7 +3430,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3449,10 +3444,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44649</v>
+        <v>45065</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3465,7 +3460,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3508,7 +3503,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3522,10 +3517,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3538,7 +3533,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3598,7 +3593,7 @@
         <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3654,7 +3649,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3664,14 +3659,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45985</v>
+        <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3684,7 +3679,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3727,7 +3722,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3741,10 +3736,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44749</v>
+        <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3757,7 +3752,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3800,7 +3795,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3814,10 +3809,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45751</v>
+        <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3830,7 +3825,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3873,7 +3868,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3946,7 +3941,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46073</v>
+        <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3976,7 +3971,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4019,7 +4014,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4033,10 +4028,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45189</v>
+        <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4048,8 +4043,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45105</v>
+        <v>46210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4121,8 +4121,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4165,7 +4170,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4179,10 +4184,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45210</v>
+        <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4195,7 +4200,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4238,7 +4243,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4248,14 +4253,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45036</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4268,7 +4273,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4311,7 +4316,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4325,10 +4330,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46139</v>
+        <v>45189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4341,7 +4346,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4384,7 +4389,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4398,10 +4403,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46210</v>
+        <v>46244</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4413,13 +4418,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>45688</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46213</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 31764-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,20 +981,25 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1009,7 +1014,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1021,6 +1026,222 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 52355-2021</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44464</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1981,58 +1981,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 52355-2021 artfynd.xlsx", "A 52355-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 52355-2021 karta.png", "A 52355-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 52355-2021 georefererad karta.tif", "A 52355-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 52355-2021 FSC-klagomål.docx", "A 52355-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 52355-2021 FSC-klagomål mail.docx", "A 52355-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 52355-2021 tillsynsbegäran.docx", "A 52355-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 52355-2021 tillsynsbegäran mail.docx", "A 52355-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2059,11 +2059,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2100,49 +2095,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2152,14 +2147,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2171,14 +2166,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2196,58 +2196,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45889</v>
+        <v>45988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2317,42 +2317,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2418,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45988</v>
+        <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2527,42 +2527,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2589,19 +2589,24 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2616,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2625,49 +2630,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2677,14 +2682,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,19 +2701,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,75 +2726,75 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>S 2231-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45688</v>
+        <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2847,59 +2847,59 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bokblombock</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/S 2231-2022 artfynd.xlsx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/S 2231-2022 karta.png", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/S 2231-2022 georefererad karta.tif", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/S 2231-2022 FSC-klagomål.docx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/S 2231-2022 FSC-klagomål mail.docx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/S 2231-2022 tillsynsbegäran.docx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/S 2231-2022 tillsynsbegäran mail.docx", "S 2231-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S 2231-2022</t>
+          <t>A 68005-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44679</v>
+        <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2936,58 +2936,26 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Bokblombock</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/S 2231-2022 artfynd.xlsx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/S 2231-2022 karta.png", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/S 2231-2022 georefererad karta.tif", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/S 2231-2022 FSC-klagomål.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/S 2231-2022 FSC-klagomål mail.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/S 2231-2022 tillsynsbegäran.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/S 2231-2022 tillsynsbegäran mail.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
+      <c r="V23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 68005-2021</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3001,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44525</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3017,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3060,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3074,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45691</v>
+        <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3089,8 +3057,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>20.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3133,7 +3106,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,10 +3120,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44749</v>
+        <v>45691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3163,7 +3136,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3206,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3220,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>46073</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3235,13 +3208,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>20.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3284,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3298,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44846</v>
+        <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3314,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3357,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3371,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3387,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3430,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3444,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45065</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3460,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3503,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3517,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45985</v>
+        <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3533,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3576,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3590,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45985</v>
+        <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3606,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3649,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3659,14 +3627,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45036</v>
+        <v>45118</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3678,8 +3646,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3722,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3736,10 +3709,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45751</v>
+        <v>44649</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3752,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3795,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3809,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46073</v>
+        <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3824,8 +3797,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3868,7 +3846,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3882,10 +3860,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3898,7 +3876,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3941,7 +3919,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3955,10 +3933,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44649</v>
+        <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3971,7 +3949,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4014,7 +3992,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4028,10 +4006,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45118</v>
+        <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4043,13 +4021,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4092,7 +4065,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4106,10 +4079,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46210</v>
+        <v>45189</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4121,13 +4094,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4187,7 +4155,7 @@
         <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4260,7 +4228,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4316,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4326,14 +4294,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45189</v>
+        <v>45036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4346,7 +4314,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4389,24 +4357,24 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>S 311-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46244</v>
+        <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4419,7 +4387,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>40.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4459,10 +4427,10 @@
       </c>
       <c r="V43" s="2" t="inlineStr"/>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 311-2025</t>
+          <t>S 1991-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4476,10 +4444,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45688</v>
+        <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4492,7 +4460,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>40.1</v>
+        <v>10.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4531,79 +4499,6 @@
         <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>S 1991-2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45688</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45373</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>46073</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45118</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44649</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45189</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45688</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45373</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>46073</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45118</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44649</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>45189</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31764-2023</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45118</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,25 +981,20 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1014,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1026,6 +1021,227 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1033,248 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45104</v>
+        <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,16 +2067,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2086,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2098,46 +2103,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2147,14 +2152,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2166,19 +2171,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2196,58 +2196,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45988</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2317,42 +2317,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45688</v>
+        <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46189</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,13 +2490,13 @@
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2523,46 +2523,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2589,24 +2589,19 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2621,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2630,49 +2625,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2682,14 +2677,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2701,14 +2696,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,51 +2726,51 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45517</v>
+        <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,13 +3057,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>20.7</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3106,7 +3101,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3120,10 +3115,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45691</v>
+        <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3179,7 +3174,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46073</v>
+        <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3204,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3247,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3261,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44909</v>
+        <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3281,8 +3276,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>20.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>46073</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>44846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46139</v>
+        <v>45065</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45065</v>
+        <v>46139</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3627,14 +3627,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45118</v>
+        <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,13 +3646,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3690,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44649</v>
+        <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3720,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3763,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3777,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46210</v>
+        <v>44909</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3797,13 +3792,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3846,7 +3836,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3860,10 +3850,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44749</v>
+        <v>44649</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3876,7 +3866,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3919,7 +3909,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3933,10 +3923,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45751</v>
+        <v>45118</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3948,8 +3938,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3992,7 +3987,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46244</v>
+        <v>46210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4021,8 +4016,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4065,7 +4065,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45189</v>
+        <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45105</v>
+        <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4211,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>45189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45036</v>
+        <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,22 +1956,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1995,49 +1990,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45889</v>
+        <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,16 +2062,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2091,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2103,46 +2098,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45373</v>
+        <v>45688</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,7 +2167,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2187,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2196,58 +2191,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,14 +2271,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,39 +2313,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,6 +2484,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2520,42 +2525,42 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2579,7 +2584,7 @@
         <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2667,7 +2672,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2677,14 +2682,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,19 +2701,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,51 +2726,51 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44749</v>
+        <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,8 +3057,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>20.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3101,7 +3106,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3115,10 +3120,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45985</v>
+        <v>45691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3131,7 +3136,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3174,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45985</v>
+        <v>44909</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3204,7 +3209,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3247,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3261,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45517</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3276,13 +3281,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46073</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44846</v>
+        <v>46073</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>45065</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46139</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3627,14 +3627,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45036</v>
+        <v>45118</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,8 +3646,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3690,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45751</v>
+        <v>44649</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3720,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3763,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44909</v>
+        <v>44749</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3793,7 +3798,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3836,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3850,10 +3855,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44649</v>
+        <v>45751</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3866,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3909,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3923,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45118</v>
+        <v>46210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3944,7 +3949,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3987,7 +3992,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46210</v>
+        <v>45189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4016,13 +4021,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4221,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45189</v>
+        <v>45036</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,253 +1249,32 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,42 +1995,42 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2049,7 +2054,7 @@
         <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2137,7 +2142,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2147,14 +2152,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2166,14 +2171,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2203,46 +2213,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2252,14 +2262,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2271,19 +2281,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2292,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2301,58 +2306,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45988</v>
+        <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,13 +2387,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2422,42 +2427,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,22 +2491,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2525,49 +2525,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46189</v>
+        <v>45988</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2637,42 +2637,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45373</v>
+        <v>46189</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,51 +2726,51 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3038,14 +3038,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45517</v>
+        <v>45036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,13 +3057,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>20.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3106,7 +3101,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3120,10 +3115,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45691</v>
+        <v>45751</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3179,7 +3174,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44909</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3208,8 +3203,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>20.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45985</v>
+        <v>45189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>44909</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46073</v>
+        <v>44846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45065</v>
+        <v>44649</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46139</v>
+        <v>45691</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45118</v>
+        <v>45065</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,13 +3646,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3690,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44649</v>
+        <v>45118</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3724,8 +3719,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44749</v>
+        <v>45105</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45751</v>
+        <v>45210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46210</v>
+        <v>45985</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3943,13 +3943,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3992,7 +3987,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45189</v>
+        <v>45985</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4022,7 +4017,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4065,7 +4060,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4079,10 +4074,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45105</v>
+        <v>46073</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4095,7 +4090,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4138,7 +4133,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4152,10 +4147,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45210</v>
+        <v>46139</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4168,7 +4163,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4211,7 +4206,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4216,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45036</v>
+        <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4240,8 +4235,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 31764-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,20 +981,25 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1009,7 +1014,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1021,6 +1026,222 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,22 +1956,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1995,42 +1990,42 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2154,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2266,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45373</v>
+        <v>45988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2282,13 +2277,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2297,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2306,51 +2301,51 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
@@ -2374,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2457,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2476,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45889</v>
+        <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2492,7 +2487,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2532,42 +2527,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45988</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2596,17 +2591,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2630,49 +2630,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46189</v>
+        <v>45373</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,51 +2726,51 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44749</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3038,14 +3038,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45036</v>
+        <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,8 +3057,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>20.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3101,7 +3106,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3115,10 +3120,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45751</v>
+        <v>46073</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3131,7 +3136,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3174,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>45691</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3203,13 +3208,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>20.7</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45189</v>
+        <v>44909</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44846</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44649</v>
+        <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45691</v>
+        <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45065</v>
+        <v>45118</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,8 +3646,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3690,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45118</v>
+        <v>44649</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3719,13 +3724,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45105</v>
+        <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3797,8 +3797,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3846,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3855,10 +3860,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45210</v>
+        <v>44749</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3876,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3919,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3933,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45985</v>
+        <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3944,7 +3949,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3987,7 +3992,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45985</v>
+        <v>45189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4017,7 +4022,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4060,7 +4065,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,10 +4079,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46073</v>
+        <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4090,7 +4095,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4133,7 +4138,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4147,10 +4152,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46139</v>
+        <v>46244</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4163,7 +4168,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4206,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46210</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4235,13 +4240,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46244</v>
+        <v>45036</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31764-2023</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45118</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,25 +981,20 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1014,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1026,6 +1021,227 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1033,248 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45104</v>
+        <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,16 +2067,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2086,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2098,46 +2103,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2147,14 +2152,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2166,19 +2171,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2196,58 +2196,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45988</v>
+        <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,16 +2277,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2313,39 +2313,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2572,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2597,16 +2597,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2630,49 +2630,49 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45373</v>
+        <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2726,51 +2726,51 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45517</v>
+        <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,13 +3057,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>20.7</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3106,7 +3101,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3120,10 +3115,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46073</v>
+        <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3179,7 +3174,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45691</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3208,8 +3203,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>20.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>44846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3627,14 +3627,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45118</v>
+        <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,13 +3646,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3690,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44649</v>
+        <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3720,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3785,7 +3780,7 @@
         <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3846,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3860,10 +3855,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44749</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3876,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3919,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3933,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45751</v>
+        <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3949,7 +3944,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3992,7 +3987,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45189</v>
+        <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4022,7 +4017,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4065,7 +4060,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4079,10 +4074,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45105</v>
+        <v>45118</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4094,8 +4089,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46244</v>
+        <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45036</v>
+        <v>45189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45688</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45118</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45118</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45688</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45118</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45118</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,22 +1956,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1995,49 +1990,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45889</v>
+        <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,16 +2062,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2091,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2103,46 +2098,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45373</v>
+        <v>45688</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,7 +2167,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2187,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2196,58 +2191,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,17 +2271,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2317,42 +2317,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45688</v>
+        <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,19 +2484,24 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2511,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2520,49 +2525,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2577,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2591,19 +2596,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,51 +2621,51 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46073</v>
+        <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,8 +3057,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>20.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3101,7 +3106,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3115,10 +3120,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44749</v>
+        <v>45691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3131,7 +3136,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3174,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>44909</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3203,13 +3208,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>20.7</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45985</v>
+        <v>46073</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44846</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46139</v>
+        <v>45065</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45065</v>
+        <v>46139</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3627,14 +3627,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45036</v>
+        <v>45118</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,8 +3646,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3690,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45751</v>
+        <v>44649</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3720,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3763,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46210</v>
+        <v>44749</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3792,13 +3797,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>45751</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44649</v>
+        <v>46210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3943,8 +3943,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3987,7 +3992,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46244</v>
+        <v>45189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4017,7 +4022,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4060,7 +4065,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,10 +4079,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45118</v>
+        <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4089,13 +4094,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45105</v>
+        <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4211,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4221,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>45036</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45189</v>
+        <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,112 +1136,112 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 31764-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>LUND</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1141,140 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45104</v>
+        <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,22 +2067,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2089,55 +2094,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45688</v>
+        <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,7 +2172,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2207,42 +2212,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2252,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2271,19 +2276,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46189</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2385,13 +2385,13 @@
         <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2418,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,24 +2484,19 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2516,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2525,49 +2520,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,14 +2572,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2596,14 +2591,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,51 +2621,51 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45517</v>
+        <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,13 +3057,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>20.7</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3106,7 +3101,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3120,10 +3115,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45691</v>
+        <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3179,7 +3174,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44909</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3208,8 +3203,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>20.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46073</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45065</v>
+        <v>44846</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46139</v>
+        <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45118</v>
+        <v>46210</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44649</v>
+        <v>45036</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44749</v>
+        <v>45751</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45751</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46210</v>
+        <v>44909</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3943,13 +3943,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3992,7 +3987,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4006,10 +4001,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45189</v>
+        <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4022,7 +4017,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4065,7 +4060,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4079,10 +4074,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45105</v>
+        <v>45118</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4094,8 +4089,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45210</v>
+        <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4211,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4221,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45036</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46244</v>
+        <v>45189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,140 +1136,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
         <v>45118</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,22 +1956,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1995,49 +1990,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45373</v>
+        <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,7 +2062,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2091,58 +2086,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45889</v>
+        <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,16 +2167,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2208,46 +2203,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,14 +2271,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,6 +2379,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2415,42 +2420,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2479,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2567,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2577,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2591,19 +2596,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,51 +2621,51 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46073</v>
+        <v>45065</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44749</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3130,8 +3130,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>20.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3174,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>45118</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3214,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>20.7</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3257,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45985</v>
+        <v>44649</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3287,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3330,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3344,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>45691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3355,7 +3360,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3415,7 +3420,7 @@
         <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3471,7 +3476,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3490,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44846</v>
+        <v>45985</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3506,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3549,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3563,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45065</v>
+        <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3579,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3622,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3631,10 +3636,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46210</v>
+        <v>44909</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,13 +3651,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45036</v>
+        <v>44749</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>45751</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>46073</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44909</v>
+        <v>45189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44649</v>
+        <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45118</v>
+        <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4089,13 +4089,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4138,7 +4133,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4152,10 +4147,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45105</v>
+        <v>46210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4167,8 +4162,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4211,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4221,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>45036</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45189</v>
+        <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,140 +1136,32 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
         <v>45118</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45688</v>
+        <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,7 +2067,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2077,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2086,58 +2091,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45104</v>
+        <v>45688</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,16 +2172,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2203,46 +2208,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2252,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2271,19 +2276,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,11 +2379,6 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2420,42 +2415,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
@@ -2479,7 +2474,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2562,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,14 +2572,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2596,14 +2591,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,51 +2621,51 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45065</v>
+        <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45118</v>
+        <v>44846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3208,13 +3208,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3257,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44649</v>
+        <v>45065</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3287,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3330,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3344,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45691</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3403,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3417,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46139</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3433,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3476,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3490,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45985</v>
+        <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3506,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3549,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3563,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45985</v>
+        <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3579,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3622,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3632,14 +3627,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44909</v>
+        <v>45036</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3652,7 +3647,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3690,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3709,10 +3704,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44749</v>
+        <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3720,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3763,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3777,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45751</v>
+        <v>44909</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3798,7 +3793,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3836,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3855,10 +3850,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46073</v>
+        <v>44649</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3866,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3909,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3923,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45189</v>
+        <v>45118</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3943,8 +3938,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4004,7 +4004,7 @@
         <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4221,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45036</v>
+        <v>45189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,28 +1956,23 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1989,7 +1984,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1998,46 +1993,46 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45373</v>
+        <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,7 +2062,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2091,58 +2086,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45688</v>
+        <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,16 +2167,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2208,46 +2203,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,14 +2271,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2418,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,19 +2484,24 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2511,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2520,49 +2525,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2577,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2591,19 +2596,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2633,39 +2633,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3038,14 +3038,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44749</v>
+        <v>45036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>45065</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3130,13 +3130,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>20.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3179,7 +3174,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3188,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44846</v>
+        <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3208,8 +3203,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>20.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45065</v>
+        <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3281,8 +3281,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3330,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3344,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>45691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3355,7 +3360,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3398,7 +3403,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3417,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>44649</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3471,7 +3476,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3490,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46139</v>
+        <v>44909</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3544,7 +3549,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3563,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46073</v>
+        <v>44749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3579,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3622,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3627,14 +3632,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45036</v>
+        <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3690,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3704,10 +3709,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45751</v>
+        <v>45985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3720,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3763,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3777,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3793,7 +3798,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3836,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3850,10 +3855,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44649</v>
+        <v>45189</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3866,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3909,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3923,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45118</v>
+        <v>45105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3938,13 +3943,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45105</v>
+        <v>45210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45210</v>
+        <v>46139</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4133,7 +4133,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46210</v>
+        <v>46073</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4162,13 +4162,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4211,7 +4206,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4225,10 +4220,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45189</v>
+        <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4240,8 +4235,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45373</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45065</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>45691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44649</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44909</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>45985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45985</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45189</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>46139</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46073</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45373</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45036</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>45065</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45517</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>45691</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>44649</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44909</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>45985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>45985</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>45189</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>46139</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46073</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>46210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,112 +1136,112 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 31764-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>LUND</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1141,140 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45373</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1981,58 +1981,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45889</v>
+        <v>46189</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2102,42 +2102,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2164,6 +2164,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -2200,49 +2205,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2252,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2271,19 +2276,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45688</v>
+        <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,28 +2486,23 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2519,7 +2514,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2528,46 +2523,46 @@
         <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46189</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,13 +2595,13 @@
         <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2621,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2633,46 +2628,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2682,14 +2677,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45988</v>
+        <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2701,8 +2696,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2738,39 +2738,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3038,14 +3038,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45036</v>
+        <v>46210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,8 +3057,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3101,7 +3106,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3115,10 +3120,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45065</v>
+        <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3131,7 +3136,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3174,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3188,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45517</v>
+        <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3203,13 +3208,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45118</v>
+        <v>46244</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3281,13 +3281,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3330,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3344,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45691</v>
+        <v>46073</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3360,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3403,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3417,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44649</v>
+        <v>45691</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3433,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3476,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3490,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44909</v>
+        <v>46139</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3566,7 +3561,7 @@
         <v>44749</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3622,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3636,10 +3631,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45751</v>
+        <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3651,8 +3646,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>20.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45985</v>
+        <v>44846</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45985</v>
+        <v>45065</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3851,14 +3851,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45189</v>
+        <v>45036</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45105</v>
+        <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45210</v>
+        <v>44909</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46139</v>
+        <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4133,7 +4133,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46073</v>
+        <v>45118</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4162,8 +4162,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4206,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4220,10 +4225,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46210</v>
+        <v>45105</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4235,13 +4240,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46244</v>
+        <v>45210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46189</v>
+        <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2102,42 +2102,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2164,11 +2164,6 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -2205,49 +2200,49 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,14 +2271,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45988</v>
+        <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2422,42 +2422,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,23 +2486,28 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2514,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2523,46 +2528,46 @@
         <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2592,22 +2597,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2619,55 +2624,55 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 59227-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2677,14 +2682,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45237</v>
+        <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,13 +2701,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2738,39 +2738,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
         <v/>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
         <v>44679</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44525</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45189</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46210</v>
+        <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>20.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45985</v>
+        <v>45691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45985</v>
+        <v>44909</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46244</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46073</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45691</v>
+        <v>46073</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46139</v>
+        <v>45065</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44749</v>
+        <v>46139</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45517</v>
+        <v>45118</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>20.7</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44846</v>
+        <v>44649</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45065</v>
+        <v>44749</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3851,14 +3851,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45036</v>
+        <v>45751</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45751</v>
+        <v>46210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3943,8 +3943,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3987,7 +3992,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4001,10 +4006,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44909</v>
+        <v>45189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4017,7 +4022,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4060,7 +4065,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4074,10 +4079,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44649</v>
+        <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4090,7 +4095,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4133,7 +4138,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4147,10 +4152,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45118</v>
+        <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4162,13 +4167,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4211,7 +4211,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4221,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45105</v>
+        <v>45036</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45210</v>
+        <v>46244</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>45688</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>46213</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE44"/>
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,112 +1136,112 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 31764-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>LUND</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1141,140 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45688</v>
+        <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,7 +2067,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2102,42 +2107,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45104</v>
+        <v>45688</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,16 +2172,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2203,46 +2208,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2252,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2271,19 +2276,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2301,58 +2301,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46189</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2385,13 +2385,13 @@
         <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2418,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,24 +2484,19 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2516,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2525,49 +2520,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,14 +2572,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2596,14 +2591,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,75 +2621,75 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59227-2025</t>
+          <t>S 2231-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45988</v>
+        <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2702,19 +2702,19 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2726,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2742,59 +2742,59 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Bokblombock</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59227-2025 artfynd.xlsx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/S 2231-2022 artfynd.xlsx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59227-2025 karta.png", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/S 2231-2022 karta.png", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59227-2025 georefererad karta.tif", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/S 2231-2022 georefererad karta.tif", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59227-2025 FSC-klagomål.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/S 2231-2022 FSC-klagomål.docx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59227-2025 FSC-klagomål mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/S 2231-2022 FSC-klagomål mail.docx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59227-2025 tillsynsbegäran.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/S 2231-2022 tillsynsbegäran.docx", "S 2231-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59227-2025 tillsynsbegäran mail.docx", "A 59227-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/S 2231-2022 tillsynsbegäran mail.docx", "S 2231-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S 2231-2022</t>
+          <t>A 68005-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44679</v>
+        <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2831,58 +2831,26 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Bokblombock</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/S 2231-2022 artfynd.xlsx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/S 2231-2022 karta.png", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/S 2231-2022 georefererad karta.tif", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/S 2231-2022 FSC-klagomål.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/S 2231-2022 FSC-klagomål mail.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/S 2231-2022 tillsynsbegäran.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/S 2231-2022 tillsynsbegäran mail.docx", "S 2231-2022")</f>
-        <v/>
-      </c>
+      <c r="V22" s="2" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 68005-2021</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2896,10 +2864,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44525</v>
+        <v>45065</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2912,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2955,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2969,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2985,7 +2953,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3028,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45517</v>
+        <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,13 +3025,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>20.7</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3106,7 +3069,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3120,10 +3083,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45691</v>
+        <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3136,7 +3099,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3179,7 +3142,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3193,10 +3156,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3209,7 +3172,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3252,7 +3215,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3266,10 +3229,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45985</v>
+        <v>44749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3282,7 +3245,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3325,7 +3288,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3339,10 +3302,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>45517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3354,8 +3317,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>20.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3398,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3412,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46073</v>
+        <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3428,7 +3396,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3471,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3485,10 +3453,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45065</v>
+        <v>44846</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3501,7 +3469,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3544,7 +3512,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3554,14 +3522,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46139</v>
+        <v>45036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3574,7 +3542,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3617,7 +3585,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3631,10 +3599,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45118</v>
+        <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3646,13 +3614,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3695,7 +3658,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3709,10 +3672,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44649</v>
+        <v>44909</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3725,7 +3688,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3768,7 +3731,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3782,10 +3745,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44749</v>
+        <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3797,8 +3760,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3841,7 +3809,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3855,10 +3823,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45751</v>
+        <v>44649</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3871,7 +3839,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3914,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3928,10 +3896,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46210</v>
+        <v>45118</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3949,7 +3917,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3992,7 +3960,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4006,10 +3974,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45189</v>
+        <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4022,7 +3990,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4082,7 +4050,7 @@
         <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4155,7 +4123,7 @@
         <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4211,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4221,14 +4189,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45036</v>
+        <v>45189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4241,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4284,24 +4252,24 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>S 311-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46244</v>
+        <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4314,7 +4282,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>40.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4354,10 +4322,10 @@
       </c>
       <c r="V42" s="2" t="inlineStr"/>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 311-2025</t>
+          <t>S 1991-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4371,10 +4339,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45688</v>
+        <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4387,7 +4355,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>40.1</v>
+        <v>10.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4426,79 +4394,6 @@
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>S 1991-2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>46213</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,22 +1956,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1995,42 +1990,42 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
@@ -2054,7 +2049,7 @@
         <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2142,7 +2137,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45688</v>
+        <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,16 +2167,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2196,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2208,46 +2203,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,14 +2271,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2301,58 +2301,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,6 +2379,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2415,42 +2420,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2479,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2567,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2577,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2591,19 +2596,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,51 +2621,51 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45065</v>
+        <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45691</v>
+        <v>45065</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46073</v>
+        <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3025,8 +3025,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>20.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3074,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3083,10 +3088,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45985</v>
+        <v>45691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3099,7 +3104,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3142,7 +3147,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45985</v>
+        <v>45118</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3171,8 +3176,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3215,7 +3225,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3229,10 +3239,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44749</v>
+        <v>44649</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3245,7 +3255,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3288,7 +3298,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3302,10 +3312,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45517</v>
+        <v>44909</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3317,13 +3327,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>20.7</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3383,7 +3388,7 @@
         <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3439,7 +3444,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44846</v>
+        <v>44749</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3469,7 +3474,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3512,7 +3517,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3522,14 +3527,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45036</v>
+        <v>45751</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3585,7 +3590,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3599,10 +3604,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45751</v>
+        <v>45189</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3615,7 +3620,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3658,7 +3663,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3672,10 +3677,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44909</v>
+        <v>45105</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3688,7 +3693,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3731,7 +3736,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46210</v>
+        <v>45210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3760,13 +3765,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44649</v>
+        <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3838,8 +3838,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3882,7 +3887,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3892,14 +3897,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45118</v>
+        <v>45036</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3911,13 +3916,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3977,7 +3977,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45105</v>
+        <v>45985</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45210</v>
+        <v>45985</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45189</v>
+        <v>46073</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,253 +1249,32 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45889</v>
+        <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,7 +2067,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2077,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2086,58 +2091,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45104</v>
+        <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,16 +2172,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2203,46 +2208,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2252,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2271,22 +2276,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2317,42 +2317,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,24 +2379,19 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2411,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2420,49 +2415,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2472,14 +2467,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2491,14 +2486,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2528,46 +2528,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45373</v>
+        <v>45688</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,51 +2621,51 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45065</v>
+        <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45691</v>
+        <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45118</v>
+        <v>44846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3176,13 +3176,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3225,7 +3220,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3239,10 +3234,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44649</v>
+        <v>45065</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3255,7 +3250,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3298,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3312,10 +3307,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44909</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3328,7 +3323,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3371,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3385,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46139</v>
+        <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3401,7 +3396,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3454,14 +3449,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44749</v>
+        <v>45036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3474,7 +3469,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3534,7 +3529,7 @@
         <v>45751</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3590,7 +3585,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3604,10 +3599,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45189</v>
+        <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3620,7 +3615,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3663,7 +3658,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3677,10 +3672,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45105</v>
+        <v>44909</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3693,7 +3688,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3736,7 +3731,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3750,10 +3745,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45210</v>
+        <v>44649</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3766,7 +3761,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3826,7 +3821,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3887,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3897,14 +3892,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45036</v>
+        <v>45118</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3916,8 +3911,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3960,7 +3960,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46244</v>
+        <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45985</v>
+        <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45985</v>
+        <v>46244</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46073</v>
+        <v>45189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45688</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45688</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45065</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45751</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44909</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44649</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45118</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>46244</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45688</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45104</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45688</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>46139</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45065</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>45751</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44909</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44649</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45118</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>46244</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 31764-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,20 +981,25 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1009,7 +1014,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1021,6 +1026,114 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,145 +1141,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
         <v>45688</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1954,11 +1954,6 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1995,49 +1990,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2047,14 +2042,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2066,14 +2061,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2091,51 +2091,51 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45104</v>
+        <v>46189</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2280,13 +2280,13 @@
         <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,19 +2379,24 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2406,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2415,49 +2420,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2467,14 +2472,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,19 +2491,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2516,51 +2516,51 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
         <v>45688</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44749</v>
+        <v>45517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2952,8 +2952,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>20.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2996,7 +3001,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45517</v>
+        <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3025,13 +3030,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>20.7</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46139</v>
+        <v>44909</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44846</v>
+        <v>46139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>45065</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3310,7 +3310,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3383,7 +3383,7 @@
         <v>45985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3449,14 +3449,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45036</v>
+        <v>45118</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3468,8 +3468,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3512,7 +3517,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3526,10 +3531,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45751</v>
+        <v>44649</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3542,7 +3547,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3602,7 +3607,7 @@
         <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3658,7 +3663,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3672,10 +3677,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44909</v>
+        <v>44749</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3688,7 +3693,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3731,7 +3736,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44649</v>
+        <v>45751</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3761,7 +3766,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3821,7 +3826,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3882,7 +3887,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3896,10 +3901,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45118</v>
+        <v>45189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3911,13 +3916,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3977,7 +3977,7 @@
         <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46244</v>
+        <v>45036</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45189</v>
+        <v>46244</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31764-2023</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45118</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,25 +981,20 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1014,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1026,6 +1021,227 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1033,248 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1954,6 +1954,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2042,14 +2047,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2061,19 +2066,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2103,46 +2103,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45889</v>
+        <v>45373</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2196,58 +2196,58 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46189</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2317,42 +2317,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,11 +2379,6 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2420,49 +2415,49 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2476,10 +2471,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45373</v>
+        <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2492,7 +2487,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2507,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2516,58 +2511,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2577,14 +2572,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2596,14 +2591,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2633,39 +2633,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44846</v>
+        <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45517</v>
+        <v>46073</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2952,13 +2952,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>20.7</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3001,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45691</v>
+        <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3031,7 +3026,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3074,7 +3069,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3088,10 +3083,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44909</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3103,8 +3098,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>20.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46139</v>
+        <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45065</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45985</v>
+        <v>44846</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45118</v>
+        <v>45065</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3468,13 +3468,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3517,7 +3512,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3527,14 +3522,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44649</v>
+        <v>45036</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3547,7 +3542,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3590,7 +3585,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3604,10 +3599,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46073</v>
+        <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3620,7 +3615,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3663,7 +3658,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3677,10 +3672,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44749</v>
+        <v>46210</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3692,8 +3687,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45751</v>
+        <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46210</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3838,13 +3838,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3887,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3901,10 +3896,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45189</v>
+        <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3917,7 +3912,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3960,7 +3955,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3974,10 +3969,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45105</v>
+        <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3989,8 +3984,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45210</v>
+        <v>45105</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45036</v>
+        <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46244</v>
+        <v>45189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,22 +1956,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1995,49 +1990,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45889</v>
+        <v>45688</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,7 +2062,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2107,42 +2102,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45373</v>
+        <v>45104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,22 +2167,22 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2199,55 +2194,55 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,14 +2271,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2313,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2379,6 +2379,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2415,42 +2420,42 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2479,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2562,7 +2567,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2577,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2591,19 +2596,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2621,51 +2621,51 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46073</v>
+        <v>45517</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2952,8 +2952,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>20.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2996,7 +3001,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3015,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44749</v>
+        <v>45691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3026,7 +3031,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3074,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3083,10 +3088,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>44909</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3098,13 +3103,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>20.7</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3164,7 +3164,7 @@
         <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3237,7 +3237,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>46073</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44846</v>
+        <v>45065</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45065</v>
+        <v>45118</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3468,8 +3468,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3512,7 +3517,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3522,14 +3527,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45036</v>
+        <v>46139</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3542,7 +3547,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3585,7 +3590,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3599,10 +3604,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45751</v>
+        <v>44649</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3615,7 +3620,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3658,7 +3663,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3672,10 +3677,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46210</v>
+        <v>44749</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3687,13 +3692,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46244</v>
+        <v>45751</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3838,8 +3838,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3882,7 +3887,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3896,10 +3901,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44649</v>
+        <v>45189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3912,7 +3917,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3955,7 +3960,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3969,10 +3974,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45118</v>
+        <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3984,13 +3989,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45105</v>
+        <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45210</v>
+        <v>45036</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45189</v>
+        <v>46244</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,112 +1136,112 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 31764-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>LUND</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1141,140 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 72269-2021</t>
+          <t>A 10617-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44543</v>
+        <v>45721</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,17 +1533,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1573,43 +1573,43 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra
-Stor häxört</t>
+          <t>Lökgroda
+Strandpadda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10617-2025</t>
+          <t>A 72269-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45721</v>
+        <v>44543</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1679,36 +1679,36 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lökgroda
-Strandpadda</t>
+          <t>Blanksvart trämyra
+Stor häxört</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45688</v>
+        <v>45889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2062,7 +2067,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2102,42 +2107,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2151,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45104</v>
+        <v>45688</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,16 +2172,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2203,39 +2208,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
@@ -2259,7 +2264,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2352,7 +2357,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2381,28 +2386,23 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2414,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2423,39 +2423,39 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
         <v>46189</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45373</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2597,22 +2597,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2624,48 +2624,48 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44846</v>
+        <v>45036</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45517</v>
+        <v>45751</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2952,13 +2952,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>20.7</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3001,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3015,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45691</v>
+        <v>44909</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3031,7 +3026,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3074,7 +3069,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3088,10 +3083,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44909</v>
+        <v>44649</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3104,7 +3099,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3147,7 +3142,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45985</v>
+        <v>45691</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3177,7 +3172,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3220,7 +3215,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3234,10 +3229,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45985</v>
+        <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3249,8 +3244,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46073</v>
+        <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45065</v>
+        <v>45105</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45118</v>
+        <v>45210</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3468,13 +3468,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3517,7 +3512,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3531,10 +3526,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46139</v>
+        <v>45985</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3547,7 +3542,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3590,7 +3585,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3604,10 +3599,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44649</v>
+        <v>45985</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3663,7 +3658,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3677,10 +3672,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44749</v>
+        <v>45189</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3693,7 +3688,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3736,7 +3731,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3750,10 +3745,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45751</v>
+        <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3766,7 +3761,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3826,7 +3821,7 @@
         <v>46210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3887,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3901,10 +3896,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45189</v>
+        <v>44749</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3917,7 +3912,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3960,7 +3955,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3974,10 +3969,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45105</v>
+        <v>45517</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3989,8 +3984,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>20.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45210</v>
+        <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45036</v>
+        <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46244</v>
+        <v>45065</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 4816-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,233 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,253 +1249,32 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45721</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>44543</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,22 +1956,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1986,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1995,49 +1990,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45889</v>
+        <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2067,7 +2062,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2082,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2091,58 +2086,58 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45688</v>
+        <v>46189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,7 +2167,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2212,42 +2207,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2252,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,19 +2271,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2318,46 +2308,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2371,10 +2361,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45373</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,22 +2377,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2414,55 +2404,55 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2472,14 +2462,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2491,14 +2481,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2528,46 +2523,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2594,6 +2589,11 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2630,42 +2630,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45036</v>
+        <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45751</v>
+        <v>45105</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44909</v>
+        <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44649</v>
+        <v>45210</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45691</v>
+        <v>45036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45118</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3244,13 +3244,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3293,7 +3288,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3307,10 +3302,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46139</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3323,7 +3318,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45105</v>
+        <v>46210</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3395,8 +3390,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45210</v>
+        <v>46244</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45985</v>
+        <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45985</v>
+        <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3614,8 +3614,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>20.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3658,7 +3663,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3672,10 +3677,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45189</v>
+        <v>45691</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3688,7 +3693,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3731,7 +3736,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3745,10 +3750,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46073</v>
+        <v>46139</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3761,7 +3766,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3804,7 +3809,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3818,10 +3823,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46210</v>
+        <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3833,13 +3838,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44749</v>
+        <v>45065</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45517</v>
+        <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>20.7</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46244</v>
+        <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44846</v>
+        <v>44749</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45065</v>
+        <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45721</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>44543</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>46189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>45105</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45210</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>46210</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46244</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45691</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>46139</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45065</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44749</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45688</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45118</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45257</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>45721</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>44543</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>46189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>45105</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>45210</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>46210</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>46244</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>45517</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45691</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>46139</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44909</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45065</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45118</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44749</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>45751</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4816-2025</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45688</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1015,12 +1015,120 @@
         <v>4</v>
       </c>
       <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>7</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>3</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1028,112 +1136,112 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 31764-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>LUND</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1141,140 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 10617-2025</t>
+          <t>A 72269-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45721</v>
+        <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1573,43 +1573,43 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Lökgroda
-Strandpadda</t>
+          <t>Blanksvart trämyra
+Stor häxört</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 72269-2021</t>
+          <t>A 10617-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44543</v>
+        <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1639,17 +1639,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1679,36 +1679,36 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra
-Stor häxört</t>
+          <t>Lökgroda
+Strandpadda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2061,23 +2061,28 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2089,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2098,39 +2103,39 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
@@ -2154,7 +2159,7 @@
         <v>46189</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2242,7 +2247,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2256,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45688</v>
+        <v>45373</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2272,7 +2277,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2287,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2296,58 +2301,58 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2361,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45688</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2377,16 +2382,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2401,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2413,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2462,14 +2467,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2481,22 +2486,17 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2527,42 +2527,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2572,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2597,16 +2597,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2630,42 +2630,42 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45189</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45105</v>
+        <v>45691</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44846</v>
+        <v>45985</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45210</v>
+        <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3152,14 +3152,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45036</v>
+        <v>44749</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45985</v>
+        <v>45517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3244,8 +3244,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>20.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3288,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>46210</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3317,8 +3322,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3361,7 +3371,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3375,10 +3385,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46210</v>
+        <v>46073</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3390,13 +3400,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3439,7 +3444,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46244</v>
+        <v>44846</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3469,7 +3474,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3512,7 +3517,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3526,10 +3531,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46073</v>
+        <v>45065</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3542,7 +3547,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3585,7 +3590,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3599,10 +3604,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45517</v>
+        <v>46244</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3614,13 +3619,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>20.7</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45691</v>
+        <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3746,14 +3746,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46139</v>
+        <v>45036</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44909</v>
+        <v>45751</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45065</v>
+        <v>44909</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45118</v>
+        <v>44649</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3984,13 +3984,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4033,7 +4028,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4042,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44649</v>
+        <v>45118</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4062,8 +4057,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44749</v>
+        <v>45105</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45751</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 59733-2023</t>
+          <t>A 31764-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45257</v>
+        <v>45118</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,20 +981,25 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1009,7 +1014,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1021,6 +1026,114 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Rosenporing
+Sydlig sotticka
+Skorpdyna
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 59733-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Backtimjan
@@ -1028,107 +1141,107 @@
 Ängsfingersvamp</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 4816-2025</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45688</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E7" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>SKÅNE LÄN</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>LUND</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>7.7</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>7</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Sydlig sotticka
@@ -1136,145 +1249,32 @@
 Strutbräken</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 31764-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenporing
-Sydlig sotticka
-Skorpdyna
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45237</v>
+        <v>45104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2059,11 +2059,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LUND</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2100,49 +2095,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2152,14 +2147,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46189</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2171,14 +2166,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2208,46 +2208,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,23 +2276,28 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2304,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2313,46 +2318,46 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2366,10 +2371,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45688</v>
+        <v>45373</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2382,7 +2387,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2397,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2406,58 +2411,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45688</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2487,16 +2492,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2511,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2523,46 +2528,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2572,14 +2577,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2591,19 +2596,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2633,39 +2633,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45189</v>
+        <v>44909</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45691</v>
+        <v>44846</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45985</v>
+        <v>45065</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45985</v>
+        <v>45517</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3098,8 +3098,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>20.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3142,7 +3147,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44749</v>
+        <v>45691</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3172,7 +3177,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3215,7 +3220,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3229,10 +3234,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45517</v>
+        <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3244,13 +3249,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46210</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3322,13 +3322,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3371,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3385,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46073</v>
+        <v>45118</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3400,8 +3395,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44846</v>
+        <v>44649</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45065</v>
+        <v>46210</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3546,8 +3546,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3590,7 +3595,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3604,10 +3609,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46244</v>
+        <v>44749</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3620,7 +3625,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3663,7 +3668,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3677,10 +3682,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46139</v>
+        <v>45751</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3693,7 +3698,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3736,7 +3741,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3746,14 +3751,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45036</v>
+        <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3766,7 +3771,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3809,7 +3814,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3823,10 +3828,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45751</v>
+        <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3839,7 +3844,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3882,7 +3887,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3896,10 +3901,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44909</v>
+        <v>45189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3912,7 +3917,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3955,7 +3960,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3969,10 +3974,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44649</v>
+        <v>45105</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3985,7 +3990,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4028,7 +4033,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4042,10 +4047,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45118</v>
+        <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4057,13 +4062,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45105</v>
+        <v>46139</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4189,14 +4189,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>45036</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 31764-2023</t>
+          <t>A 59733-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45118</v>
+        <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -981,25 +981,20 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1014,7 +1009,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1026,6 +1021,227 @@
         <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Backtimjan
+Scharlakansvaxing
+Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 4816-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Sydlig sotticka
+Guldlockmossa
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 31764-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LUND</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenporing
 Sydlig sotticka
@@ -1033,248 +1249,32 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 31764-2023 artfynd.xlsx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 31764-2023 karta.png", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 31764-2023 georefererad karta.tif", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 31764-2023 FSC-klagomål.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 31764-2023 FSC-klagomål mail.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 31764-2023 tillsynsbegäran.docx", "A 31764-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 31764-2023 tillsynsbegäran mail.docx", "A 31764-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 59733-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Backtimjan
-Scharlakansvaxing
-Ängsfingersvamp</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 59733-2023 artfynd.xlsx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 59733-2023 karta.png", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 59733-2023 georefererad karta.tif", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 59733-2023 FSC-klagomål.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 59733-2023 FSC-klagomål mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 59733-2023 tillsynsbegäran.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 59733-2023 tillsynsbegäran mail.docx", "A 59733-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 4816-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45688</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>LUND</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Sydlig sotticka
-Guldlockmossa
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4816-2025 artfynd.xlsx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4816-2025 karta.png", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4816-2025 georefererad karta.tif", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4816-2025 FSC-klagomål.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4816-2025 FSC-klagomål mail.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4816-2025 tillsynsbegäran.docx", "A 4816-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4816-2025 tillsynsbegäran mail.docx", "A 4816-2025")</f>
         <v/>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 72269-2021</t>
+          <t>A 10617-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44543</v>
+        <v>45721</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,17 +1533,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1573,43 +1573,43 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra
-Stor häxört</t>
+          <t>Lökgroda
+Strandpadda</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10617-2025</t>
+          <t>A 72269-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45721</v>
+        <v>44543</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1679,36 +1679,36 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Lökgroda
-Strandpadda</t>
+          <t>Blanksvart trämyra
+Stor häxört</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45104</v>
+        <v>45237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2059,6 +2059,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>LUND</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2095,49 +2100,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2147,14 +2152,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2166,19 +2171,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2208,46 +2208,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2282,16 +2282,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2306,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2315,49 +2315,49 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45373</v>
+        <v>46189</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2411,58 +2411,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45688</v>
+        <v>45373</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2516,58 +2516,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46189</v>
+        <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,13 +2600,13 @@
         <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2633,39 +2633,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44909</v>
+        <v>45036</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44846</v>
+        <v>45751</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45065</v>
+        <v>44909</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45517</v>
+        <v>44649</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3098,13 +3098,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>20.7</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3147,7 +3142,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3161,10 +3156,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45691</v>
+        <v>45985</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3177,7 +3172,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3237,7 +3232,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3293,7 +3288,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3307,10 +3302,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45985</v>
+        <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3322,8 +3317,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45118</v>
+        <v>45105</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3395,13 +3395,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44649</v>
+        <v>45691</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3474,7 +3469,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3517,7 +3512,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3531,10 +3526,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46210</v>
+        <v>45210</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3546,13 +3541,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3595,7 +3585,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3609,10 +3599,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44749</v>
+        <v>45189</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3625,7 +3615,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3668,7 +3658,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3682,10 +3672,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45751</v>
+        <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3698,7 +3688,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3741,7 +3731,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3755,10 +3745,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46073</v>
+        <v>46210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3770,8 +3760,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3831,7 +3826,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3887,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3901,10 +3896,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45189</v>
+        <v>46139</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3917,7 +3912,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3960,7 +3955,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3974,10 +3969,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45105</v>
+        <v>44749</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3990,7 +3985,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4033,7 +4028,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4047,10 +4042,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45210</v>
+        <v>45517</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4062,8 +4057,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>20.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46139</v>
+        <v>44846</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4189,14 +4189,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45036</v>
+        <v>45065</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt LUND.xlsx
+++ b/Översikt LUND.xlsx
@@ -601,7 +601,7 @@
         <v>44533</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46213</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45688</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45118</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>45630</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>46213</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 10617-2025</t>
+          <t>A 72269-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1513,14 +1513,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45721</v>
+        <v>44543</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1573,43 +1573,43 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Lökgroda
-Strandpadda</t>
+          <t>Blanksvart trämyra
+Stor häxört</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 72269-2021</t>
+          <t>A 10617-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1619,14 +1619,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44543</v>
+        <v>45721</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1639,17 +1639,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1679,36 +1679,36 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra
-Stor häxört</t>
+          <t>Lökgroda
+Strandpadda</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 72269-2021 artfynd.xlsx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 10617-2025 artfynd.xlsx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 72269-2021 karta.png", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 10617-2025 karta.png", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 72269-2021 georefererad karta.tif", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 10617-2025 georefererad karta.tif", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 72269-2021 FSC-klagomål.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 10617-2025 FSC-klagomål.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 72269-2021 FSC-klagomål mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 10617-2025 FSC-klagomål mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 72269-2021 tillsynsbegäran.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 10617-2025 tillsynsbegäran.docx", "A 10617-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 72269-2021 tillsynsbegäran mail.docx", "A 72269-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 10617-2025 tillsynsbegäran mail.docx", "A 10617-2025")</f>
         <v/>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>45714</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>46213</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 39260-2025</t>
+          <t>A 55158-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45889</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,17 +1956,22 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1981,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1990,49 +1995,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55158-2023</t>
+          <t>A 11732-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45237</v>
+        <v>45373</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2061,28 +2066,23 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2103,46 +2103,46 @@
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dvärgjohannesört</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55158-2023 artfynd.xlsx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55158-2023 karta.png", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55158-2023 georefererad karta.tif", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55158-2023 FSC-klagomål.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55158-2023 FSC-klagomål mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55158-2023 tillsynsbegäran.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55158-2023 tillsynsbegäran mail.docx", "A 55158-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4746-2025</t>
+          <t>A 39260-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45688</v>
+        <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2212,42 +2212,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 39260-2025 artfynd.xlsx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 39260-2025 karta.png", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 39260-2025 georefererad karta.tif", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 39260-2025 FSC-klagomål.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 39260-2025 FSC-klagomål mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 39260-2025 tillsynsbegäran.docx", "A 39260-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 39260-2025 tillsynsbegäran mail.docx", "A 39260-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55145-2023</t>
+          <t>A 4746-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2257,14 +2257,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45688</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,19 +2276,14 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2318,46 +2313,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 4746-2025 artfynd.xlsx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 4746-2025 karta.png", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 4746-2025 georefererad karta.tif", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 4746-2025 FSC-klagomål.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 4746-2025 FSC-klagomål mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 4746-2025 tillsynsbegäran.docx", "A 4746-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 4746-2025 tillsynsbegäran mail.docx", "A 4746-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27377-2026</t>
+          <t>A 29075-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2371,10 +2366,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46189</v>
+        <v>45104</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2390,13 +2385,13 @@
         <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2411,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2423,46 +2418,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ätlig groda</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11732-2024</t>
+          <t>A 55145-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2472,14 +2467,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45373</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2491,14 +2486,19 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2516,58 +2516,58 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Dvärgjohannesört</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 11732-2024 artfynd.xlsx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 55145-2023 artfynd.xlsx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 11732-2024 karta.png", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 55145-2023 karta.png", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 11732-2024 georefererad karta.tif", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 55145-2023 georefererad karta.tif", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 11732-2024 FSC-klagomål.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 55145-2023 FSC-klagomål.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 11732-2024 FSC-klagomål mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 55145-2023 FSC-klagomål mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 11732-2024 tillsynsbegäran.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 55145-2023 tillsynsbegäran.docx", "A 55145-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 11732-2024 tillsynsbegäran mail.docx", "A 11732-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 55145-2023 tillsynsbegäran mail.docx", "A 55145-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 29075-2023</t>
+          <t>A 27377-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45104</v>
+        <v>46189</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2600,13 +2600,13 @@
         <v>0.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2633,39 +2633,39 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ätlig groda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 29075-2023 artfynd.xlsx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/artfynd/A 27377-2026 artfynd.xlsx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 29075-2023 karta.png", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor/A 27377-2026 karta.png", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 29075-2023 georefererad karta.tif", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/kartor_geotiff/A 27377-2026 georefererad karta.tif", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 29075-2023 FSC-klagomål.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomål/A 27377-2026 FSC-klagomål.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 29075-2023 FSC-klagomål mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/klagomålsmail/A 27377-2026 FSC-klagomål mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 29075-2023 tillsynsbegäran.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsyn/A 27377-2026 tillsynsbegäran.docx", "A 27377-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 29075-2023 tillsynsbegäran mail.docx", "A 29075-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1281/tillsynsmail/A 27377-2026 tillsynsbegäran mail.docx", "A 27377-2026")</f>
         <v/>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
         <v>44679</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>44525</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 17519-2023</t>
+          <t>A 5059-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45036</v>
+        <v>45691</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16499-2025</t>
+          <t>A 28885-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45751</v>
+        <v>44749</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2996,7 +2996,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59918-2022</t>
+          <t>A 32972-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44909</v>
+        <v>45517</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3025,8 +3025,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>20.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3074,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13754-2022</t>
+          <t>A 9889-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3083,10 +3088,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44649</v>
+        <v>46073</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3099,7 +3104,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3142,7 +3147,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58335-2025</t>
+          <t>A 45725-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3156,10 +3161,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45985</v>
+        <v>44846</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3172,7 +3177,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3215,7 +3220,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58337-2025</t>
+          <t>A 58335-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3232,7 +3237,7 @@
         <v>45985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3245,7 +3250,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3288,7 +3293,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31773-2023</t>
+          <t>A 58337-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45118</v>
+        <v>45985</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3317,13 +3322,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 29083-2023</t>
+          <t>A 21767-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45105</v>
+        <v>45065</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5059-2025</t>
+          <t>A 17519-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3449,14 +3449,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45691</v>
+        <v>45036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 49297-2023</t>
+          <t>A 20277-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45210</v>
+        <v>46139</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44646-2023</t>
+          <t>A 16499-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45189</v>
+        <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9889-2026</t>
+          <t>A 59918-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46073</v>
+        <v>44909</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30506-2026</t>
+          <t>A 13754-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46210</v>
+        <v>44649</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3760,13 +3760,8 @@
           <t>LUND</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3809,7 +3804,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33019-2026</t>
+          <t>A 31773-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3823,10 +3818,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46244</v>
+        <v>45118</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3838,8 +3833,13 @@
           <t>LUND</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20277-2026</t>
+          <t>A 29083-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46139</v>
+        <v>45105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 28885-2022</t>
+          <t>A 49297-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44749</v>
+        <v>45210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4028,7 +4028,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32972-2024</t>
+          <t>A 30506-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45517</v>
+        <v>46210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>20.7</v>
+        <v>6.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 45725-2022</t>
+          <t>A 44646-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44846</v>
+        <v>45189</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21767-2023</t>
+          <t>A 33019-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45065</v>
+        <v>46244</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>45688</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>46213</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
